--- a/Day5/官网知识库/01_官网页面来源与审核记录.xlsx
+++ b/Day5/官网知识库/01_官网页面来源与审核记录.xlsx
@@ -619,7 +619,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>静态</t>
+          <t>低频更新</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -632,7 +632,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>页面可能包含不同年份的统计资料。回答学生人数、学院数量、专业数量等问题时，应明确统计年份并与较新的学校简介或官方概况页面交叉核对，不能无条件作为当前实时数据依据。</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
@@ -847,12 +851,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>《河海大学章程》获教育部核准</t>
+          <t>河海大学校训</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>https://www.hhu.edu.cn/2015/0409/c13911a124950/page.htm</t>
+          <t>https://www.hhu.edu.cn/_t129/2021/0326/c179a220940/page.psp</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -867,7 +871,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>良</t>
+          <t>优</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +889,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>页面介绍河海大学校训及其内涵，适合回答校训含义等稳定性问题。</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
@@ -1255,17 +1263,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>河海校历与VPN指南</t>
+          <t>信息化服务报修平台</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>https://xsc.hhu.edu.cn/2023/0223/c4711a257143/page.htm</t>
+          <t>https://hhic.hhu.edu.cn/wlbz/list.htm</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>学生处</t>
+          <t>河海大学信息化建设管理处</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1273,11 +1281,7 @@
           <t>校园公共服务</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2023-02-23</t>
-        </is>
-      </c>
+      <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>低频更新</t>
@@ -1293,7 +1297,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>页面提供校园网络、邮箱、一卡通、软件正版化等信息化系统问题的报修入口和处理方式，适合回答信息化服务故障如何报修等实用问题。报修平台本身需要校内身份认证，但服务说明页面为公开访问。</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
@@ -1606,12 +1614,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>借还书流程</t>
+          <t>中外文书刊借阅管理规则</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>https://library.hhu.edu.cn/news/show-318.html</t>
+          <t>https://library.hhu.edu.cn/news/show-169.html</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1624,15 +1632,19 @@
           <t>图书馆服务</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2022-03-04</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>静态</t>
+          <t>低频更新</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>良</t>
+          <t>优</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1640,7 +1652,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>页面明确说明本科生、研究生和教职工的借阅册数、借阅期限、异校区借还、预约与委托借阅等规定。规则具有低频更新属性，后续应关注图书馆是否发布新修订版本。</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
@@ -2166,7 +2182,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>https://gs.hhu.edu.cn/_t186/3581/list.htm</t>
+          <t>https://gs.hhu.edu.cn/17283/list.htm</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2187,7 +2203,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>良</t>
+          <t>优</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2195,7 +2211,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>栏目包含不同年份和不同类型的研究生培养方案。回答时应说明方案年份、培养层次和适用对象，避免将某一年度或某一类型方案概括为全部研究生的统一要求。</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
@@ -2484,7 +2504,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>低频更新</t>
+          <t>历史批次</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2497,7 +2517,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J40" s="2" t="n"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>仅用于回答2024年涉外法治微专业招生简章中的内容，不能据此判断当前是否仍在招生。涉及当前招生状态时应查询最新年度通知。</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
@@ -2537,7 +2561,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>低频更新</t>
+          <t>历史批次</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2550,7 +2574,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J41" s="2" t="n"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>仅用于回答2025年数字孪生水利微专业招生简章中的内容，不能据此判断当前是否仍可报名。涉及当前招生状态时应查询最新年度通知。</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
@@ -2590,7 +2618,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>高频更新</t>
+          <t>年度更新</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2603,7 +2631,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J42" s="2" t="n"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>2026年现行研究生招生咨询联系方式。联系方式和院系安排具有年度时效，后续招生年度应替换为最新联系方式。</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
@@ -2667,12 +2699,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>河海大学2025年各院系招生咨询联系方式</t>
+          <t>河海大学2026年硕士研究生招生简章</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>https://gs.hhu.edu.cn/_t186/2025/0219/c3515a298808/page.htm</t>
+          <t>https://gs.hhu.edu.cn/2025/0930/c17277a308113/page.htm</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2687,17 +2719,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>高频更新</t>
+          <t>年度更新</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>良</t>
+          <t>优</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2705,7 +2737,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J44" s="2" t="n"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>仅适用于河海大学2026年硕士研究生招生，包含招生专业、报考条件、报名考试和录取等信息。招生简章具有年度时效，后续应按招生年度替换为最新版本。</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
@@ -2760,7 +2796,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026年现行招生章程。招生政策具有年度时效，后续应按年度复核并优先使用最新章程。原2013年页面和2024年页面已被替换。</t>
+          <t>该资料仅对应2026年本科招生政策。招生章程按年度更新，后续应优先使用最新招生年度版本。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2924,7 +2960,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>外国语学院研究生招生宣讲</t>
+          <t>外国语学院2025年研究生招生宣讲会</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2944,12 +2980,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>低频更新</t>
+          <t>历史事件</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2962,7 +2998,11 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>仅用于回答外国语学院面向2025年研究生招生开展的该次宣讲活动。不代表当前招生政策、招生安排或现行联系方式。涉及当前招生信息时应查询最新招生简章和学院通知。</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
           <t>孙凤摇</t>
